--- a/docs/access/roles_matrix_20261012.xlsx
+++ b/docs/access/roles_matrix_20261012.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeyazarov/Desktop/AUTOPROFI ECOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4983CD-0A6E-5340-8917-204A896973FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1B4EC8-C14E-5946-8995-2238D1674142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Права доступа" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="280">
   <si>
     <t>Права доступа к сайту ТД АВТОПРОФИ: функции по ролям</t>
   </si>
@@ -1086,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1131,9 +1131,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1166,224 +1163,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1792,21 +1572,21 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="4" spans="1:15" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -1893,23 +1673,23 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
@@ -1959,23 +1739,23 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
@@ -3172,23 +2952,23 @@
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
@@ -3661,23 +3441,23 @@
       <c r="O49" s="9"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="24"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="23"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
@@ -4170,23 +3950,23 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
-      <c r="J63" s="24"/>
-      <c r="K63" s="24"/>
-      <c r="L63" s="24"/>
-      <c r="M63" s="24"/>
-      <c r="N63" s="24"/>
-      <c r="O63" s="24"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="23"/>
+      <c r="K63" s="23"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="23"/>
+      <c r="N63" s="23"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
@@ -4585,23 +4365,23 @@
       <c r="O73" s="9"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
-      <c r="K74" s="24"/>
-      <c r="L74" s="24"/>
-      <c r="M74" s="24"/>
-      <c r="N74" s="24"/>
-      <c r="O74" s="24"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
@@ -4994,23 +4774,23 @@
       <c r="O84" s="9"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="24"/>
-      <c r="H85" s="24"/>
-      <c r="I85" s="24"/>
-      <c r="J85" s="24"/>
-      <c r="K85" s="24"/>
-      <c r="L85" s="24"/>
-      <c r="M85" s="24"/>
-      <c r="N85" s="24"/>
-      <c r="O85" s="24"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="23"/>
+      <c r="J85" s="23"/>
+      <c r="K85" s="23"/>
+      <c r="L85" s="23"/>
+      <c r="M85" s="23"/>
+      <c r="N85" s="23"/>
+      <c r="O85" s="23"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
@@ -5643,23 +5423,23 @@
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="B102" s="24"/>
-      <c r="C102" s="24"/>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="24"/>
-      <c r="H102" s="24"/>
-      <c r="I102" s="24"/>
-      <c r="J102" s="24"/>
-      <c r="K102" s="24"/>
-      <c r="L102" s="24"/>
-      <c r="M102" s="24"/>
-      <c r="N102" s="24"/>
-      <c r="O102" s="24"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23"/>
+      <c r="M102" s="23"/>
+      <c r="N102" s="23"/>
+      <c r="O102" s="23"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
@@ -5924,23 +5704,23 @@
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A109" s="23" t="s">
+      <c r="A109" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="24"/>
-      <c r="H109" s="24"/>
-      <c r="I109" s="24"/>
-      <c r="J109" s="24"/>
-      <c r="K109" s="24"/>
-      <c r="L109" s="24"/>
-      <c r="M109" s="24"/>
-      <c r="N109" s="24"/>
-      <c r="O109" s="24"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23"/>
+      <c r="E109" s="23"/>
+      <c r="F109" s="23"/>
+      <c r="G109" s="23"/>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+      <c r="L109" s="23"/>
+      <c r="M109" s="23"/>
+      <c r="N109" s="23"/>
+      <c r="O109" s="23"/>
     </row>
     <row r="110" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
@@ -6081,224 +5861,44 @@
   </sheetData>
   <autoFilter ref="A4:M113" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="A63:O63"/>
+    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="A85:O85"/>
+    <mergeCell ref="A102:O102"/>
+    <mergeCell ref="A109:O109"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A37:O37"/>
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="A50:O50"/>
-    <mergeCell ref="A63:O63"/>
-    <mergeCell ref="A74:O74"/>
-    <mergeCell ref="A85:O85"/>
-    <mergeCell ref="A102:O102"/>
-    <mergeCell ref="A109:O109"/>
   </mergeCells>
-  <conditionalFormatting sqref="H7:N7 H38:N49 H9:N36 H51:N62 H64:N73 H75:N84 H86:N101 H103:N108 H110:N113">
-    <cfRule type="cellIs" dxfId="43" priority="44" operator="equal">
+  <conditionalFormatting sqref="H7:O7">
+    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14 O16 O20:O21 O38:O49 O52:O59 O64:O73 O75:O84 O89:O97 O106 O110:O113 O100">
-    <cfRule type="cellIs" dxfId="41" priority="41" operator="equal">
+  <conditionalFormatting sqref="H9:O36">
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7">
-    <cfRule type="cellIs" dxfId="40" priority="40" operator="equal">
+  <conditionalFormatting sqref="H38:O49 H64:O73 H75:O84 H110:O113">
+    <cfRule type="cellIs" dxfId="10" priority="41" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
-    <cfRule type="cellIs" dxfId="39" priority="39" operator="equal">
+  <conditionalFormatting sqref="H51:O62">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O10">
-    <cfRule type="cellIs" dxfId="38" priority="38" operator="equal">
+  <conditionalFormatting sqref="H86:O101">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11">
-    <cfRule type="cellIs" dxfId="37" priority="37" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O12">
-    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O13">
-    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O15">
-    <cfRule type="cellIs" dxfId="34" priority="34" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O17">
-    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O18">
-    <cfRule type="cellIs" dxfId="32" priority="32" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O19">
-    <cfRule type="cellIs" dxfId="31" priority="31" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O22">
-    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O23">
-    <cfRule type="cellIs" dxfId="29" priority="29" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O24">
-    <cfRule type="cellIs" dxfId="28" priority="28" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O25">
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O26">
-    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O27">
-    <cfRule type="cellIs" dxfId="25" priority="25" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O28">
-    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O29">
-    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O30">
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O31">
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O32">
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O33">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O34">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O35">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O36">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O60">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O51">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O61">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O62">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O86">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O87">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O88">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O98">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O99">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O101">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O103">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O104">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O105">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O107">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O108">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="H103:O108">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6313,36 +5913,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="10" width="15" customWidth="1"/>
+    <col min="5" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="4" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="4" spans="1:12" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -6355,196 +5958,306 @@
       <c r="D4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="16" t="str">
-        <f>'Права доступа'!H4</f>
-        <v>Администратор</v>
-      </c>
-      <c r="F4" s="16" t="str">
-        <f>'Права доступа'!I4</f>
-        <v>РОП</v>
-      </c>
-      <c r="G4" s="16" t="str">
-        <f>'Права доступа'!J4</f>
-        <v>Продакт</v>
-      </c>
-      <c r="H4" s="16" t="str">
-        <f>'Права доступа'!K4</f>
-        <v>Маркетинг</v>
-      </c>
-      <c r="I4" s="16" t="str">
-        <f>'Права доступа'!L4</f>
-        <v>Менеджер WB</v>
-      </c>
-      <c r="J4" s="16" t="str">
-        <f>'Права доступа'!M4</f>
-        <v>Менеджер OZ</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="17">
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>245</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>247</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="17">
+      <c r="J6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>107</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
+      <c r="K7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>251</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="17">
+      <c r="F8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>254</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
+      <c r="F9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="17" t="s">
         <v>256</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="17">
+      <c r="F10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>258</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="F11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:J11">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L8">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E5:J11" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K7:K11 L8 E5:J11" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"✓"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6561,78 +6274,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
     </row>
     <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
+      <c r="A14" s="19"/>
     </row>
     <row r="15" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>272</v>
       </c>
     </row>
